--- a/data/trans_orig/P42C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P42C-Estudios-trans_orig.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -525,25 +525,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde tuvo lugar dicha consulta ginecológica en 2012</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última consulta ginecológica en 2012 (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +547,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -563,17 +556,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -644,41 +626,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -701,13 +648,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -722,37 +662,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>114</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123619</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>104039</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>145313</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105636</t>
+          <t>104039</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146425</t>
+          <t>145313</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,47 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>123619</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>105636</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>146425</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>12,73%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -835,37 +740,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>793</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>847533</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>825839</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>867113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>824727</t>
+          <t>825839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>865516</t>
+          <t>867113</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,47 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>793</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>847533</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>824727</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>865516</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>87,27%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>84,92%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>89,12%</t>
+          <t>89,29%</t>
         </is>
       </c>
     </row>
@@ -948,37 +818,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>907</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>971152</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>971152</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>971152</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1012,41 +882,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>907</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>971152</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>971152</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>971152</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1065,37 +900,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>311</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>346959</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>316378</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>381250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>311976</t>
+          <t>316378</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>382756</t>
+          <t>381250</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,47 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>346959</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>311976</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>382756</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>25,46%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>22,89%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>28,09%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -1178,37 +978,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>943</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1015815</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>981524</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1046396</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>980018</t>
+          <t>981524</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1050798</t>
+          <t>1046396</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,47 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>943</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1015815</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>980018</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1050798</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>74,54%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>71,91%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>77,11%</t>
+          <t>76,78%</t>
         </is>
       </c>
     </row>
@@ -1291,37 +1056,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1362774</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1362774</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1362774</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1355,41 +1120,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1254</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1362774</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1362774</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1362774</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1408,37 +1138,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>162</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184152</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>164224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>206794</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>163862</t>
+          <t>164224</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>206405</t>
+          <t>206794</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,47 +1198,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>184152</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>163862</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>206405</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>45,68%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>40,65%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>51,2%</t>
+          <t>51,3%</t>
         </is>
       </c>
     </row>
@@ -1521,37 +1216,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>198</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>218986</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>196344</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>238914</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>196733</t>
+          <t>196344</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>239276</t>
+          <t>238914</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,47 +1276,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>218986</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>196733</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>239276</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>54,32%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>48,8%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>59,35%</t>
+          <t>59,26%</t>
         </is>
       </c>
     </row>
@@ -1634,37 +1294,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>360</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>403138</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>403138</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>403138</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1698,41 +1358,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>403138</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>403138</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>403138</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1751,37 +1376,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>587</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>654730</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>606560</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>699938</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>610321</t>
+          <t>606560</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>702000</t>
+          <t>699938</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,47 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>654730</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>610321</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>702000</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>23,92%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>22,3%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>25,65%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -1864,37 +1454,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2082334</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2037126</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2130504</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2035064</t>
+          <t>2037126</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2126743</t>
+          <t>2130504</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,47 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1934</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2082334</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>2035064</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2126743</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>76,08%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>74,35%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>77,7%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>
@@ -1977,37 +1532,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2737064</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2737064</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2737064</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2041,41 +1596,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>2521</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>2737064</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>2737064</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>2737064</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2089,13 +1609,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -2109,7 +1628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2128,25 +1647,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde tuvo lugar dicha consulta ginecológica en 2016</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última consulta ginecológica en 2016 (tasa de respuesta: 98,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +1669,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2166,17 +1678,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -2247,41 +1748,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -2304,13 +1770,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2325,37 +1784,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24976</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15602</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35742</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +1829,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16043</t>
+          <t>15602</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38685</t>
+          <t>35742</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,47 +1844,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>24976</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>16043</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>38685</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>5,59%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -2438,37 +1862,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>606</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>667593</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>656827</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>676967</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +1907,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>653884</t>
+          <t>656827</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>676526</t>
+          <t>676967</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,47 +1922,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>667593</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>653884</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>676526</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,39%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>94,41%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>97,68%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -2551,37 +1940,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>628</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692569</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692569</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>692569</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2615,41 +2004,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>692569</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>692569</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>692569</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -2668,37 +2022,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>212</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>226350</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>196415</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>254093</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2067,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>197814</t>
+          <t>196415</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>256159</t>
+          <t>254093</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,47 +2082,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>226350</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>197814</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>256159</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>14,22%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>12,43%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>16,09%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -2781,37 +2100,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1365558</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1337815</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1395493</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2145,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1335749</t>
+          <t>1337815</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1394094</t>
+          <t>1395493</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,47 +2160,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1311</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1365558</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1335749</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1394094</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>85,78%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>83,91%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>87,57%</t>
+          <t>87,66%</t>
         </is>
       </c>
     </row>
@@ -2894,37 +2178,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1523</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1591908</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1591908</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1591908</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2958,41 +2242,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1523</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1591908</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1591908</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1591908</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3011,37 +2260,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>169</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>176779</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>156764</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>198181</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +2305,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>156926</t>
+          <t>156764</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>198690</t>
+          <t>198181</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,47 +2320,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>176779</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>156926</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>198690</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>36,68%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>32,56%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>41,23%</t>
+          <t>41,12%</t>
         </is>
       </c>
     </row>
@@ -3124,37 +2338,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>292</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>305132</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>283730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325147</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +2383,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>283221</t>
+          <t>283730</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324985</t>
+          <t>325147</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,47 +2398,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>292</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>305132</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>283221</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>324985</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>63,32%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>58,77%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>67,44%</t>
+          <t>67,47%</t>
         </is>
       </c>
     </row>
@@ -3237,37 +2416,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>461</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>481911</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>481911</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>481911</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3301,41 +2480,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>481911</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>481911</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>481911</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3354,37 +2498,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>403</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>428105</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>392731</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>466845</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +2543,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>391241</t>
+          <t>392731</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>467917</t>
+          <t>466845</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,47 +2558,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>428105</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>391241</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>467917</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>15,48%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>14,14%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>16,91%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -3467,37 +2576,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2338283</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2299543</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2373657</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +2621,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2298471</t>
+          <t>2299543</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2375147</t>
+          <t>2373657</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,47 +2636,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2209</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2338283</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>2298471</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2375147</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>84,52%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>83,09%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>85,86%</t>
+          <t>85,8%</t>
         </is>
       </c>
     </row>
@@ -3580,37 +2654,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2766388</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2766388</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2766388</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -3644,41 +2718,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>2612</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>2766388</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>2766388</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>2766388</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -3692,13 +2731,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
@@ -3712,7 +2750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3731,25 +2769,18 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
-    <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el lugar donde tuvo lugar dicha consulta ginecológica en 2023</t>
+          <t>Población según si era asistencia pública o privada donde le realizaron la última consulta ginecológica en 2023 (tasa de respuesta: 99,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +2791,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3769,17 +2800,6 @@
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
-      <c r="T1" s="3" t="n"/>
-      <c r="U1" s="3" t="n"/>
-      <c r="V1" s="3" t="n"/>
-      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -3850,41 +2870,6 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
-        <is>
-          <t>lím sup IC</t>
-        </is>
-      </c>
-      <c r="Q2" s="3" t="inlineStr">
-        <is>
-          <t>n (muestra)</t>
-        </is>
-      </c>
-      <c r="R2" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím inf IC)</t>
-        </is>
-      </c>
-      <c r="T2" s="3" t="inlineStr">
-        <is>
-          <t>N (lím sup IC)</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>Estimación puntual</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>lím inf IC</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -3907,13 +2892,6 @@
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n"/>
-      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -3928,37 +2906,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27075</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19987</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37914</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +2951,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19715</t>
+          <t>19987</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38467</t>
+          <t>37914</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,47 +2966,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>27075</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>19715</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>38467</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>8,89%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -4041,37 +2984,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>776</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>405581</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>394742</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>412669</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +3029,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>394189</t>
+          <t>394742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>412941</t>
+          <t>412669</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,47 +3044,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>776</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>405581</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>394189</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>412941</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>93,74%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>91,11%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>95,44%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -4154,37 +3062,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>823</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>432656</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>432656</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>432656</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4218,41 +3126,6 @@
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>823</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>432656</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>432656</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>432656</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4271,37 +3144,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>363</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>243778</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>192355</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>275078</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +3189,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>199406</t>
+          <t>192355</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>275856</t>
+          <t>275078</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,47 +3204,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>243778</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>199406</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>275856</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>20,7%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>16,93%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>23,42%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -4384,37 +3222,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>933901</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>902601</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>985324</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +3267,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>901823</t>
+          <t>902601</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>978273</t>
+          <t>985324</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,47 +3282,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1355</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>933901</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>901823</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>978273</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>79,3%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>76,58%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>83,07%</t>
+          <t>83,67%</t>
         </is>
       </c>
     </row>
@@ -4497,37 +3300,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1177679</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1177679</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1177679</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4561,41 +3364,6 @@
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1718</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1177679</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1177679</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1177679</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4614,37 +3382,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>299</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>195146</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>177835</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>213119</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +3427,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>176799</t>
+          <t>177835</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>211935</t>
+          <t>213119</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,47 +3442,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>195146</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>176799</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>211935</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>48,62%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>44,05%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>52,8%</t>
+          <t>53,1%</t>
         </is>
       </c>
     </row>
@@ -4727,37 +3460,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>333</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>206217</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>188244</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>223528</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +3505,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>189428</t>
+          <t>188244</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>224564</t>
+          <t>223528</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,47 +3520,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>206217</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>189428</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>224564</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>51,38%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>47,2%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>55,95%</t>
+          <t>55,69%</t>
         </is>
       </c>
     </row>
@@ -4840,37 +3538,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>632</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>401363</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>401363</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>401363</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4904,41 +3602,6 @@
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>401363</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>401363</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>401363</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -4957,37 +3620,37 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>709</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>465999</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>417385</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>507420</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +3665,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>409851</t>
+          <t>417385</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>505398</t>
+          <t>507420</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,47 +3680,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>709</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>465999</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>409851</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>505398</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>23,16%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>20,37%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>25,12%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -5070,37 +3698,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2464</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1545699</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1504278</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1594313</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +3743,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1506300</t>
+          <t>1504278</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1601847</t>
+          <t>1594313</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,47 +3758,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2464</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1545699</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1506300</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1601847</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>76,84%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>74,88%</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>79,63%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -5183,37 +3776,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2011698</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2011698</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2011698</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5247,41 +3840,6 @@
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>3173</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>2011698</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>2011698</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>2011698</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -5295,13 +3853,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="Q1:W1"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>

--- a/data/trans_orig/P42C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P42C-Estudios-trans_orig.xlsx
@@ -672,12 +672,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104039</t>
+          <t>103108</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>145313</t>
+          <t>146465</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -687,12 +687,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>104039</t>
+          <t>103108</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>145313</t>
+          <t>146465</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -750,12 +750,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>825839</t>
+          <t>824687</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>867113</t>
+          <t>868044</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>825839</t>
+          <t>824687</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>867113</t>
+          <t>868044</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>316378</t>
+          <t>315045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>381250</t>
+          <t>382117</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -925,12 +925,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -945,12 +945,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>316378</t>
+          <t>315045</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>381250</t>
+          <t>382117</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -988,12 +988,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>981524</t>
+          <t>980657</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1046396</t>
+          <t>1047729</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>981524</t>
+          <t>980657</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1046396</t>
+          <t>1047729</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>76,88%</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>164224</t>
+          <t>164011</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>206794</t>
+          <t>204481</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>164224</t>
+          <t>164011</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>206794</t>
+          <t>204481</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>50,72%</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>196344</t>
+          <t>198657</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>238914</t>
+          <t>239127</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>196344</t>
+          <t>198657</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>238914</t>
+          <t>239127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>606560</t>
+          <t>611600</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>699938</t>
+          <t>705222</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>606560</t>
+          <t>611600</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>699938</t>
+          <t>705222</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1436,12 +1436,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2037126</t>
+          <t>2031842</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2130504</t>
+          <t>2125464</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2037126</t>
+          <t>2031842</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2130504</t>
+          <t>2125464</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,65%</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15602</t>
+          <t>16012</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35742</t>
+          <t>37391</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15602</t>
+          <t>16012</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35742</t>
+          <t>37391</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>656827</t>
+          <t>655178</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>676967</t>
+          <t>676557</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>656827</t>
+          <t>655178</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>676967</t>
+          <t>676557</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>196415</t>
+          <t>200075</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>254093</t>
+          <t>256992</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>196415</t>
+          <t>200075</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>254093</t>
+          <t>256992</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1337815</t>
+          <t>1334916</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1395493</t>
+          <t>1391833</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1337815</t>
+          <t>1334916</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1395493</t>
+          <t>1391833</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,43%</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156764</t>
+          <t>155623</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>198181</t>
+          <t>199554</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>156764</t>
+          <t>155623</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>198181</t>
+          <t>199554</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>41,41%</t>
         </is>
       </c>
     </row>
@@ -2348,12 +2348,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>283730</t>
+          <t>282357</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>325147</t>
+          <t>326288</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>283730</t>
+          <t>282357</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>325147</t>
+          <t>326288</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,71%</t>
         </is>
       </c>
     </row>
@@ -2508,12 +2508,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>392731</t>
+          <t>391040</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>466845</t>
+          <t>467693</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2543,12 +2543,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>392731</t>
+          <t>391040</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>466845</t>
+          <t>467693</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2299543</t>
+          <t>2298695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2373657</t>
+          <t>2375348</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2299543</t>
+          <t>2298695</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2373657</t>
+          <t>2375348</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,86%</t>
         </is>
       </c>
     </row>
@@ -2911,22 +2911,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27075</t>
+          <t>28742</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19987</t>
+          <t>21595</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37914</t>
+          <t>38068</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27075</t>
+          <t>28742</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19987</t>
+          <t>21595</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37914</t>
+          <t>38068</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -2989,27 +2989,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>405581</t>
+          <t>438207</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>394742</t>
+          <t>428881</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>412669</t>
+          <t>445354</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3024,27 +3024,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>405581</t>
+          <t>438207</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>394742</t>
+          <t>428881</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>412669</t>
+          <t>445354</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3067,17 +3067,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>432656</t>
+          <t>466949</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>432656</t>
+          <t>466949</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>432656</t>
+          <t>466949</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3102,17 +3102,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>432656</t>
+          <t>466949</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>432656</t>
+          <t>466949</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>432656</t>
+          <t>466949</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>243778</t>
+          <t>268747</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>192355</t>
+          <t>244079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>275078</t>
+          <t>295614</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>243778</t>
+          <t>268747</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>192355</t>
+          <t>244079</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>275078</t>
+          <t>295614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>933901</t>
+          <t>923479</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>902601</t>
+          <t>896612</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>985324</t>
+          <t>948147</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>933901</t>
+          <t>923479</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>902601</t>
+          <t>896612</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>985324</t>
+          <t>948147</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>77,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>79,53%</t>
         </is>
       </c>
     </row>
@@ -3305,17 +3305,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1177679</t>
+          <t>1192226</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1177679</t>
+          <t>1192226</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1177679</t>
+          <t>1192226</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1177679</t>
+          <t>1192226</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1177679</t>
+          <t>1192226</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1177679</t>
+          <t>1192226</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3387,32 +3387,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>195146</t>
+          <t>213974</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>177835</t>
+          <t>194434</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>213119</t>
+          <t>230821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3422,32 +3422,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>195146</t>
+          <t>213974</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>177835</t>
+          <t>194434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>213119</t>
+          <t>230821</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>51,6%</t>
         </is>
       </c>
     </row>
@@ -3465,32 +3465,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>206217</t>
+          <t>233379</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>188244</t>
+          <t>216532</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>223528</t>
+          <t>252919</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3500,32 +3500,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>206217</t>
+          <t>233379</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>188244</t>
+          <t>216532</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>223528</t>
+          <t>252919</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>56,54%</t>
         </is>
       </c>
     </row>
@@ -3543,17 +3543,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>401363</t>
+          <t>447353</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>401363</t>
+          <t>447353</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>401363</t>
+          <t>447353</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3578,17 +3578,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>401363</t>
+          <t>447353</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>401363</t>
+          <t>447353</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>401363</t>
+          <t>447353</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3625,32 +3625,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>465999</t>
+          <t>511463</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>417385</t>
+          <t>475366</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>507420</t>
+          <t>544883</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3660,32 +3660,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>465999</t>
+          <t>511463</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>417385</t>
+          <t>475366</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>507420</t>
+          <t>544883</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -3703,32 +3703,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1545699</t>
+          <t>1595065</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1504278</t>
+          <t>1561645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1594313</t>
+          <t>1631162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3738,32 +3738,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1545699</t>
+          <t>1595065</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1504278</t>
+          <t>1561645</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1594313</t>
+          <t>1631162</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>77,43%</t>
         </is>
       </c>
     </row>
@@ -3781,17 +3781,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2011698</t>
+          <t>2106528</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2011698</t>
+          <t>2106528</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2011698</t>
+          <t>2106528</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3816,17 +3816,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2011698</t>
+          <t>2106528</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2011698</t>
+          <t>2106528</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2011698</t>
+          <t>2106528</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
